--- a/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición</t>
+          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128,36; 137,34</t>
+          <t>128,55; 137,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125,07; 136,46</t>
+          <t>124,58; 136,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143,56; 157,89</t>
+          <t>143,27; 158,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127,53; 138,03</t>
+          <t>127,89; 137,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>128,55; 138,43</t>
+          <t>128,86; 139,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>126,5; 141,67</t>
+          <t>126,38; 142,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>129,59; 136,3</t>
+          <t>129,45; 136,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>128,77; 136,7</t>
+          <t>128,6; 136,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135,72; 147,79</t>
+          <t>136,01; 147,91</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>127,63; 131,58</t>
+          <t>127,59; 131,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132,04; 135,65</t>
+          <t>132,14; 136,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,51; 147,34</t>
+          <t>132,27; 146,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128,15; 132,68</t>
+          <t>128,48; 132,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>130,78; 134,71</t>
+          <t>130,58; 134,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>137,55; 144,21</t>
+          <t>137,72; 144,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>128,72; 131,82</t>
+          <t>128,66; 131,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>131,78; 134,61</t>
+          <t>131,87; 134,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136,59; 143,93</t>
+          <t>136,42; 144,01</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122,66; 129,6</t>
+          <t>122,28; 129,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123,28; 130,36</t>
+          <t>123,35; 130,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132,3; 142,23</t>
+          <t>133,15; 142,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,24; 131,23</t>
+          <t>124,55; 131,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126,51; 133,7</t>
+          <t>126,53; 133,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,56; 144,96</t>
+          <t>135,43; 145,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,55; 129,49</t>
+          <t>124,32; 129,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>125,89; 130,86</t>
+          <t>125,78; 130,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136,0; 142,67</t>
+          <t>135,9; 142,81</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>127,5; 130,83</t>
+          <t>127,54; 130,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>130,51; 133,66</t>
+          <t>130,44; 133,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135,08; 146,4</t>
+          <t>135,15; 145,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,54; 132,16</t>
+          <t>128,48; 132,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>130,54; 133,79</t>
+          <t>130,52; 133,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>137,77; 142,73</t>
+          <t>137,86; 143,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,62; 130,97</t>
+          <t>128,63; 130,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,92; 133,24</t>
+          <t>130,94; 133,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137,38; 142,95</t>
+          <t>137,44; 142,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
+          <t>Talla media, en centímetros, recogida por medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128,55; 137,23</t>
+          <t>128,58; 137,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>124,58; 136,69</t>
+          <t>125,03; 137,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143,27; 158,52</t>
+          <t>142,95; 157,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127,89; 137,92</t>
+          <t>127,7; 137,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>128,86; 139,0</t>
+          <t>129,22; 139,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>126,38; 142,1</t>
+          <t>126,55; 141,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>129,45; 136,47</t>
+          <t>129,76; 136,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>128,6; 136,55</t>
+          <t>129,0; 136,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>136,01; 147,91</t>
+          <t>136,63; 148,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>127,59; 131,71</t>
+          <t>127,4; 131,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132,14; 136,0</t>
+          <t>132,22; 135,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,27; 146,55</t>
+          <t>131,94; 147,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128,48; 132,66</t>
+          <t>128,35; 132,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>130,58; 134,65</t>
+          <t>130,57; 134,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>137,72; 144,0</t>
+          <t>137,85; 144,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>128,66; 131,54</t>
+          <t>128,6; 131,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>131,87; 134,64</t>
+          <t>131,96; 134,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136,42; 144,01</t>
+          <t>136,69; 144,88</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122,28; 129,5</t>
+          <t>122,45; 129,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123,35; 130,52</t>
+          <t>123,39; 130,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133,15; 142,67</t>
+          <t>133,25; 142,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,55; 131,8</t>
+          <t>124,31; 131,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126,53; 133,48</t>
+          <t>126,52; 133,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,43; 145,67</t>
+          <t>135,67; 145,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,32; 129,69</t>
+          <t>124,58; 129,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>125,78; 130,97</t>
+          <t>125,96; 130,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135,9; 142,81</t>
+          <t>136,23; 142,57</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>127,54; 130,88</t>
+          <t>127,44; 130,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>130,44; 133,69</t>
+          <t>130,37; 133,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135,15; 145,07</t>
+          <t>135,48; 147,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,48; 132,03</t>
+          <t>128,53; 131,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>130,52; 133,84</t>
+          <t>130,42; 133,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>137,86; 143,05</t>
+          <t>137,61; 142,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,63; 130,92</t>
+          <t>128,59; 130,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,94; 133,26</t>
+          <t>130,96; 133,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137,44; 142,69</t>
+          <t>137,26; 143,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>132,92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>133,9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>135,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>132,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>131,28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>150,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>132,92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>133,9</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>133,95</t>
+          <t>149,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>141,51</t>
+          <t>141,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>128,58; 137,17</t>
+          <t>127,53; 138,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125,03; 137,04</t>
+          <t>128,55; 138,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142,95; 157,95</t>
+          <t>127,9; 143,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127,7; 137,97</t>
+          <t>128,36; 137,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>129,22; 139,52</t>
+          <t>125,07; 136,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>126,55; 141,54</t>
+          <t>143,06; 155,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>129,76; 136,41</t>
+          <t>129,59; 136,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>129,0; 136,84</t>
+          <t>128,77; 136,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>136,63; 148,46</t>
+          <t>135,47; 146,42</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130,56</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>132,61</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142,07</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>129,55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>134,03</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>137,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>130,56</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>132,61</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>140,83</t>
+          <t>135,8</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139,45</t>
+          <t>139,36</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>127,4; 131,54</t>
+          <t>128,15; 132,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>132,22; 135,81</t>
+          <t>130,78; 134,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131,94; 147,0</t>
+          <t>138,8; 145,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128,35; 132,78</t>
+          <t>127,63; 131,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>130,57; 134,68</t>
+          <t>132,04; 135,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>137,85; 144,29</t>
+          <t>132,32; 139,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>128,6; 131,52</t>
+          <t>128,72; 131,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>131,96; 134,64</t>
+          <t>131,78; 134,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136,69; 144,88</t>
+          <t>137,03; 141,48</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>127,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>129,94</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>142,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>126,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>126,83</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>137,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>127,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>129,94</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>140,77</t>
+          <t>139,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139,47</t>
+          <t>140,73</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122,45; 129,88</t>
+          <t>124,24; 131,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123,39; 130,11</t>
+          <t>126,51; 133,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133,25; 142,53</t>
+          <t>137,43; 146,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,31; 131,92</t>
+          <t>122,66; 129,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126,52; 133,59</t>
+          <t>123,28; 130,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>135,67; 145,72</t>
+          <t>133,45; 143,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,58; 129,4</t>
+          <t>124,55; 129,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>125,96; 130,75</t>
+          <t>125,89; 130,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136,23; 142,57</t>
+          <t>137,35; 143,74</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>130,26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132,13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>141,6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>129,2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>132,08</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>138,88</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>130,26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>140,26</t>
+          <t>137,77</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139,63</t>
+          <t>139,89</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>127,44; 130,91</t>
+          <t>128,54; 132,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>130,37; 133,71</t>
+          <t>130,54; 133,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135,48; 147,16</t>
+          <t>139,17; 143,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,53; 131,87</t>
+          <t>127,5; 130,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>130,42; 133,75</t>
+          <t>130,51; 133,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>137,61; 142,73</t>
+          <t>135,22; 140,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,59; 130,91</t>
+          <t>128,62; 130,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,96; 133,38</t>
+          <t>130,92; 133,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137,26; 143,32</t>
+          <t>138,14; 141,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>132,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>133,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>135,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>132,97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>131,28</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>149,36</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>132,95</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>132,75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>141,64</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>132.9151296411573</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>133.8985056397035</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>135.5668933643396</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>132.9732867140173</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>131.2840279660223</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>149.3558150828248</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>132.9451005672915</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>132.7487182904192</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>141.6353335540003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>127,53; 138,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>128,55; 138,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127,9; 143,25</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>128,36; 137,34</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>125,07; 136,46</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>143,06; 155,69</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>129,59; 136,3</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128,77; 136,7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135,47; 146,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>127.5321552637402</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>128.5491934127872</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>127.8969988530059</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>128.3563457979758</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>125.0739351126535</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>143.0625713192429</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>129.5896449793394</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>128.7689446198123</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>135.4661546973215</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>138.0319294800567</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>138.4256130006685</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>143.249988534237</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>137.3421373712076</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>136.4555499508604</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>155.6874086460804</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>136.2981836805972</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>136.6966274991342</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>146.4218687888581</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>130,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>132,61</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>142,07</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>129,55</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>134,03</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>135,8</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>130,08</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>133,29</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>128,15; 132,68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>130,78; 134,71</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>138,8; 145,22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>127,63; 131,58</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>132,04; 135,65</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>132,32; 139,13</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>128,72; 131,82</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>131,78; 134,61</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>137,03; 141,48</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>130.5585094818422</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>132.6143076351143</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>142.0709034119156</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>129.5536695807669</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>134.0250088212984</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>135.8016429620747</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>130.0784668768834</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>133.2942884849379</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>139.3603249886395</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>127,96</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>129,94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>142,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126,06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>126,83</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>139,1</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>127,01</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>128,44</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>140,73</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>128.1482896633512</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>130.7761710964926</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>138.7988745897067</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>127.6309559830146</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>132.0417269869542</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>132.317412534096</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>128.7183255744913</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>131.7813881145648</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>137.0278765291248</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>124,24; 131,23</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126,51; 133,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>137,43; 146,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>122,66; 129,6</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>123,28; 130,36</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>133,45; 143,13</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>124,55; 129,49</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>125,89; 130,86</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>137,35; 143,74</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>132.6796997346462</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>134.7074423559317</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>145.2188371236983</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>131.5846442361863</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>135.6533112920959</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>139.1300495882563</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>131.8154246389206</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>134.6058818458696</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>141.4827790719632</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>130,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>132,13</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>141,6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>129,2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132,08</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>137,77</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>129,74</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132,11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>139,89</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>127.9568008184239</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>129.9429878781599</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>142.2323559645005</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>126.0594459127105</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>126.8282016980494</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>139.1034660018659</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>127.0117097493342</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>128.4429755680468</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>140.7250142618628</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>128,54; 132,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>130,54; 133,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139,17; 143,97</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>127,5; 130,83</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>130,51; 133,66</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>135,22; 140,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>128,62; 130,97</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>130,92; 133,24</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>138,14; 141,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>124.2438301004753</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>126.5086828439603</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>137.4270572567501</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>122.6605104272361</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>123.2848753174756</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>133.4512822187135</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>124.5519166314389</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>125.8902877368038</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>137.3496630883932</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>131.2304552993315</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>133.6959295079421</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>146.3646086360005</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>129.6022054436185</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>130.3614192965499</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>143.1343366113456</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>129.4934906326708</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>130.8602241802251</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>143.7443612694905</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>130.2619540268768</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>132.126185039651</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>141.5953066873152</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>129.2002785025321</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>132.082728575989</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>137.7734827016792</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>129.7447413676716</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>132.1054200025506</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>139.8917331575554</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>128.5424729988246</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>130.5365812752016</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>139.1681920408439</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>127.503702981282</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>130.5102806614116</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>135.2245978178786</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>128.6174917802447</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>130.9228089995232</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>138.1372570759099</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>132.1618556494758</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>133.7879126949009</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>143.9689690384212</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>130.8320922549772</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>133.6635327835879</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>140.5210363204991</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>130.9703755487198</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>133.2420242039933</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>141.7018548324504</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
